--- a/outputs/unpatched_all_results.xlsx
+++ b/outputs/unpatched_all_results.xlsx
@@ -468,20 +468,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4.782866910099983</v>
+        <v>5.50665371119976</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9938503593368969</v>
+        <v>1.034068434070141</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9690348982810975</v>
+        <v>0.9612958550453186</v>
       </c>
       <c r="F2" t="n">
-        <v>0.02043911821068023</v>
+        <v>0.02656126428804035</v>
       </c>
     </row>
     <row r="3">
@@ -492,20 +492,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.816980883479118</v>
+        <v>5.640318691730499</v>
       </c>
       <c r="D3" t="n">
-        <v>1.253126896110832</v>
+        <v>1.152904912195762</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9683208346366883</v>
+        <v>0.9575774550437928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02647662838946208</v>
+        <v>0.02346370756159655</v>
       </c>
     </row>
     <row r="4">
@@ -516,20 +516,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.015451945364475</v>
+        <v>5.780973434448242</v>
       </c>
       <c r="D4" t="n">
-        <v>1.614482039942419</v>
+        <v>1.070723210766899</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9699641823768616</v>
+        <v>0.9521645069122314</v>
       </c>
       <c r="F4" t="n">
-        <v>0.01741903731308592</v>
+        <v>0.03076388009495369</v>
       </c>
     </row>
     <row r="5">
@@ -540,20 +540,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.119224786758423</v>
+        <v>5.90051680803299</v>
       </c>
       <c r="D5" t="n">
-        <v>1.830456832696435</v>
+        <v>1.770259567731462</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9648540735244751</v>
+        <v>0.9527002453804017</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02769114022239381</v>
+        <v>0.03390856544537157</v>
       </c>
     </row>
     <row r="6">
@@ -564,20 +564,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.139940716326237</v>
+        <v>5.924487411975861</v>
       </c>
       <c r="D6" t="n">
-        <v>1.645400103193869</v>
+        <v>1.458038585570786</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9618404150009155</v>
+        <v>0.951429295539856</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0313601753033708</v>
+        <v>0.03025003713232196</v>
       </c>
     </row>
     <row r="7">
@@ -588,20 +588,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.256057344377041</v>
+        <v>5.961481779813766</v>
       </c>
       <c r="D7" t="n">
-        <v>1.905788144229434</v>
+        <v>1.261883682082291</v>
       </c>
       <c r="E7" t="n">
-        <v>0.953877854347229</v>
+        <v>0.9452078223228455</v>
       </c>
       <c r="F7" t="n">
-        <v>0.03213596474438223</v>
+        <v>0.04711577368614275</v>
       </c>
     </row>
     <row r="8">
@@ -612,20 +612,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.285005643963814</v>
+        <v>6.217490583658218</v>
       </c>
       <c r="D8" t="n">
-        <v>2.542293912000506</v>
+        <v>1.190048222539151</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9549591541290283</v>
+        <v>0.9421149611473083</v>
       </c>
       <c r="F8" t="n">
-        <v>0.04176659644529655</v>
+        <v>0.03589994121327282</v>
       </c>
     </row>
     <row r="9">
@@ -636,20 +636,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>5.326892994344234</v>
+        <v>6.492022126913071</v>
       </c>
       <c r="D9" t="n">
-        <v>2.309781985974117</v>
+        <v>1.494057233936337</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9584339261054993</v>
+        <v>0.9492428064346313</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02784351870531096</v>
+        <v>0.02784754560149493</v>
       </c>
     </row>
     <row r="10">
@@ -660,20 +660,20 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5.362526811659336</v>
+        <v>6.524828523397446</v>
       </c>
       <c r="D10" t="n">
-        <v>1.815672230224645</v>
+        <v>1.565476972776844</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9656142830848694</v>
+        <v>0.9475290179252625</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02518017637028598</v>
+        <v>0.03423353549148182</v>
       </c>
     </row>
     <row r="11">
@@ -688,16 +688,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.393654592335224</v>
+        <v>6.632690355181694</v>
       </c>
       <c r="D11" t="n">
-        <v>2.442450435012594</v>
+        <v>1.755025746944123</v>
       </c>
       <c r="E11" t="n">
-        <v>0.955994701385498</v>
+        <v>0.9465335965156555</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0396651627008837</v>
+        <v>0.02301774144036346</v>
       </c>
     </row>
     <row r="12">
@@ -708,20 +708,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.407735593616962</v>
+        <v>6.666989848017693</v>
       </c>
       <c r="D12" t="n">
-        <v>1.928225329199953</v>
+        <v>1.704876321591726</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9552194476127625</v>
+        <v>0.9434340238571167</v>
       </c>
       <c r="F12" t="n">
-        <v>0.03361729631523584</v>
+        <v>0.02652755949965933</v>
       </c>
     </row>
     <row r="13">
@@ -732,20 +732,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>5.512292049825191</v>
+        <v>6.717895865440369</v>
       </c>
       <c r="D13" t="n">
-        <v>2.314468752314253</v>
+        <v>1.737102959945265</v>
       </c>
       <c r="E13" t="n">
-        <v>0.955816388130188</v>
+        <v>0.94048672914505</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02916109354873933</v>
+        <v>0.03176939909076333</v>
       </c>
     </row>
     <row r="14">
@@ -756,20 +756,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.608198381960392</v>
+        <v>6.74177311360836</v>
       </c>
       <c r="D14" t="n">
-        <v>2.471196543032108</v>
+        <v>2.235041234654103</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9559101104736328</v>
+        <v>0.9300442576408386</v>
       </c>
       <c r="F14" t="n">
-        <v>0.03385498918208237</v>
+        <v>0.0469824309358675</v>
       </c>
     </row>
     <row r="15">
@@ -780,20 +780,20 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.718377530574799</v>
+        <v>6.787012740969658</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9135242008192225</v>
+        <v>1.597101739112367</v>
       </c>
       <c r="E15" t="n">
-        <v>0.948194682598114</v>
+        <v>0.9432553291320801</v>
       </c>
       <c r="F15" t="n">
-        <v>0.03828937955684879</v>
+        <v>0.03663828716865566</v>
       </c>
     </row>
     <row r="16">
@@ -804,20 +804,20 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.740262381732464</v>
+        <v>6.818801090121269</v>
       </c>
       <c r="D16" t="n">
-        <v>2.192377981473521</v>
+        <v>2.187827427810285</v>
       </c>
       <c r="E16" t="n">
-        <v>0.95082026720047</v>
+        <v>0.9338300466537476</v>
       </c>
       <c r="F16" t="n">
-        <v>0.03437381710178105</v>
+        <v>0.04920025315796138</v>
       </c>
     </row>
     <row r="17">
@@ -828,92 +828,92 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.846507847309113</v>
+        <v>6.89887747168541</v>
       </c>
       <c r="D17" t="n">
-        <v>1.93566720125329</v>
+        <v>1.722571531915536</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9626391768455506</v>
+        <v>0.9386795878410339</v>
       </c>
       <c r="F17" t="n">
-        <v>0.02362896955108583</v>
+        <v>0.03646236225425867</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"length_scale": 1.0, "noise": 1.0, "alpha": 1e-06}</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.853546522557735</v>
+        <v>6.966905505521997</v>
       </c>
       <c r="D18" t="n">
-        <v>2.416785570105366</v>
+        <v>1.883068303448421</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9563320398330688</v>
+        <v>0.9332498384841745</v>
       </c>
       <c r="F18" t="n">
-        <v>0.03423612250527276</v>
+        <v>0.03266223567480146</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GaussianProcess</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"length_scale": 1.0, "noise": 0.1, "alpha": 1e-06}</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.883816294372082</v>
+        <v>6.966908984050929</v>
       </c>
       <c r="D19" t="n">
-        <v>2.595382324682367</v>
+        <v>1.883068252139846</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9559612989425659</v>
+        <v>0.9332497238294518</v>
       </c>
       <c r="F19" t="n">
-        <v>0.02495985978839165</v>
+        <v>0.03266236906771333</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 10.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.939909070730209</v>
+        <v>7.016028612852097</v>
       </c>
       <c r="D20" t="n">
-        <v>2.37798514646904</v>
+        <v>2.098190125683114</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9651089668273926</v>
+        <v>0.9308850884437561</v>
       </c>
       <c r="F20" t="n">
-        <v>0.01706608492677041</v>
+        <v>0.03923562077287737</v>
       </c>
     </row>
     <row r="21">
@@ -924,212 +924,212 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>6.15920402109623</v>
+        <v>7.153329253196716</v>
       </c>
       <c r="D21" t="n">
-        <v>2.780155003045991</v>
+        <v>1.635793952437218</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9595120668411254</v>
+        <v>0.9365772366523742</v>
       </c>
       <c r="F21" t="n">
-        <v>0.02974948770953758</v>
+        <v>0.03815314469721666</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{"degree": 2, "alpha": 1.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "elu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6.220473125576973</v>
+        <v>7.187610939145088</v>
       </c>
       <c r="D22" t="n">
-        <v>2.887169008347467</v>
+        <v>1.250570484117068</v>
       </c>
       <c r="E22" t="n">
-        <v>0.96398366689682</v>
+        <v>0.9449093818664551</v>
       </c>
       <c r="F22" t="n">
-        <v>0.02027305308455603</v>
+        <v>0.03335817000227454</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{"degree": 2, "alpha": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>6.265989318490028</v>
+        <v>7.198473885655403</v>
       </c>
       <c r="D23" t="n">
-        <v>2.947002247707904</v>
+        <v>1.716726321937138</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9640872478485107</v>
+        <v>0.9426293253898621</v>
       </c>
       <c r="F23" t="n">
-        <v>0.02078951118329205</v>
+        <v>0.03606000416515968</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{"length_scale": 1.0, "noise": 0.1, "alpha": 1e-06}</t>
+          <t>{"degree": 2, "alpha": 0.1}</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.349227618489612</v>
+        <v>7.511232420802116</v>
       </c>
       <c r="D24" t="n">
-        <v>3.155697444712513</v>
+        <v>1.437879477724647</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9618532787247716</v>
+        <v>0.9307578563690185</v>
       </c>
       <c r="F24" t="n">
-        <v>0.02587004599348607</v>
+        <v>0.0312123863372179</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GaussianProcess</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{"length_scale": 1.0, "noise": 1.0, "alpha": 1e-06}</t>
+          <t>{"degree": 2, "alpha": 1.0}</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>6.34923011659335</v>
+        <v>7.52787247300148</v>
       </c>
       <c r="D25" t="n">
-        <v>3.155699362461966</v>
+        <v>1.411009582250182</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9618532491921531</v>
+        <v>0.9304431080818176</v>
       </c>
       <c r="F25" t="n">
-        <v>0.02587007441498796</v>
+        <v>0.03038226622169974</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{"degree": 2, "alpha": 10.0}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>6.370261721313</v>
+        <v>7.835819497704506</v>
       </c>
       <c r="D26" t="n">
-        <v>2.479659309541948</v>
+        <v>2.310663611852126</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9585339784622192</v>
+        <v>0.9153546690940857</v>
       </c>
       <c r="F26" t="n">
-        <v>0.02019203342754703</v>
+        <v>0.04305560836049246</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "selu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"degree": 2, "alpha": 10.0}</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6.545683071017265</v>
+        <v>8.090848252177238</v>
       </c>
       <c r="D27" t="n">
-        <v>2.442995084790516</v>
+        <v>1.404947466684189</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9508798360824585</v>
+        <v>0.9249964952468872</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02743787610872827</v>
+        <v>0.02812668618278084</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KAN</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>7.282314226031303</v>
+        <v>8.091798052191734</v>
       </c>
       <c r="D28" t="n">
-        <v>2.400404767574668</v>
+        <v>2.780191682361731</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9452667713165284</v>
+        <v>0.9047032952308655</v>
       </c>
       <c r="F28" t="n">
-        <v>0.04004188309400268</v>
+        <v>0.05857815643821652</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>7.374360138310176</v>
+        <v>8.213370442390442</v>
       </c>
       <c r="D29" t="n">
-        <v>2.241938914283633</v>
+        <v>2.770025773026465</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9579787810706442</v>
+        <v>0.912663733959198</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01974789372605842</v>
+        <v>0.04306141976446252</v>
       </c>
     </row>
     <row r="30">
@@ -1140,140 +1140,140 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.515418827533722</v>
+        <v>8.275810778141022</v>
       </c>
       <c r="D30" t="n">
-        <v>2.530251855093786</v>
+        <v>2.169636939577213</v>
       </c>
       <c r="E30" t="n">
-        <v>0.942306923866272</v>
+        <v>0.9129591345787048</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0365568973167946</v>
+        <v>0.04140048695330537</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>7.539526102180014</v>
+        <v>8.343108370900154</v>
       </c>
       <c r="D31" t="n">
-        <v>3.060531906373418</v>
+        <v>2.070429262966892</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9397538318805185</v>
+        <v>0.9116542100906372</v>
       </c>
       <c r="F31" t="n">
-        <v>0.04918803237603444</v>
+        <v>0.0484689588752058</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>KAN</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"width": [16, 1], "grid_size": 5, "spline_order": 3, "learning_rate": 0.01}</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>7.593771912194486</v>
+        <v>8.409733325242996</v>
       </c>
       <c r="D32" t="n">
-        <v>1.733584880180292</v>
+        <v>2.163743933716832</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9568875721815246</v>
+        <v>0.8989832401275635</v>
       </c>
       <c r="F32" t="n">
-        <v>0.01367143789939781</v>
+        <v>0.06656993046331683</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.603145688772202</v>
+        <v>8.523493436924294</v>
       </c>
       <c r="D33" t="n">
-        <v>3.217642648714869</v>
+        <v>0.7234285220634195</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9416366219520569</v>
+        <v>0.9247806284409418</v>
       </c>
       <c r="F33" t="n">
-        <v>0.03833411175506806</v>
+        <v>0.03153142074738097</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.5, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>7.638242170214653</v>
+        <v>8.767273590675307</v>
       </c>
       <c r="D34" t="n">
-        <v>3.170285855809935</v>
+        <v>0.8070633476338802</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9303500533103943</v>
+        <v>0.9223879775453598</v>
       </c>
       <c r="F34" t="n">
-        <v>0.03664668054534168</v>
+        <v>0.03214396897351602</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>7.643579767255181</v>
+        <v>8.779680356383324</v>
       </c>
       <c r="D35" t="n">
-        <v>1.919470349721432</v>
+        <v>2.316519428312722</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9571653331182635</v>
+        <v>0.9023252725601196</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01408664439792702</v>
+        <v>0.0552180138966674</v>
       </c>
     </row>
     <row r="36">
@@ -1284,116 +1284,116 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>7.649224996566772</v>
+        <v>8.811095654964447</v>
       </c>
       <c r="D36" t="n">
-        <v>3.205092814651442</v>
+        <v>1.324948881825239</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9411697149276733</v>
+        <v>0.9109225630760193</v>
       </c>
       <c r="F36" t="n">
-        <v>0.03792079992686134</v>
+        <v>0.03481170301999695</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>7.710982908536442</v>
+        <v>8.849419355392456</v>
       </c>
       <c r="D37" t="n">
-        <v>3.620450631550238</v>
+        <v>2.098537458628567</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9351344382437581</v>
+        <v>0.9002526521682739</v>
       </c>
       <c r="F37" t="n">
-        <v>0.05673829170574511</v>
+        <v>0.05988717759739468</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 1.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>7.739069536328316</v>
+        <v>8.863004595041275</v>
       </c>
       <c r="D38" t="n">
-        <v>5.874876003981223</v>
+        <v>2.269251503317926</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9406976103782654</v>
+        <v>0.9047391057014466</v>
       </c>
       <c r="F38" t="n">
-        <v>0.06692153967207823</v>
+        <v>0.06204252285252516</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>7.766341282893322</v>
+        <v>8.98267462849617</v>
       </c>
       <c r="D39" t="n">
-        <v>1.636692386473887</v>
+        <v>2.632625460063363</v>
       </c>
       <c r="E39" t="n">
-        <v>0.9525410181033243</v>
+        <v>0.9010227918624878</v>
       </c>
       <c r="F39" t="n">
-        <v>0.01400336623800744</v>
+        <v>0.04942386414529083</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>7.809041514992714</v>
+        <v>9.023765138171095</v>
       </c>
       <c r="D40" t="n">
-        <v>2.592952377065467</v>
+        <v>2.659086924221477</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9553568720817566</v>
+        <v>0.8796402007102602</v>
       </c>
       <c r="F40" t="n">
-        <v>0.02131773598063856</v>
+        <v>0.06877786097418001</v>
       </c>
     </row>
     <row r="41">
@@ -1404,44 +1404,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7.825166508555412</v>
+        <v>9.047123938798904</v>
       </c>
       <c r="D41" t="n">
-        <v>3.532065776487122</v>
+        <v>2.323450594726486</v>
       </c>
       <c r="E41" t="n">
-        <v>0.9432760596275329</v>
+        <v>0.8992295026779175</v>
       </c>
       <c r="F41" t="n">
-        <v>0.04202581690484467</v>
+        <v>0.06188133431165516</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>7.960181459784508</v>
+        <v>9.105471298098564</v>
       </c>
       <c r="D42" t="n">
-        <v>2.262552958774797</v>
+        <v>2.44936404015884</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9542585372924804</v>
+        <v>0.8937487363815307</v>
       </c>
       <c r="F42" t="n">
-        <v>0.01757799001852734</v>
+        <v>0.07128461417599867</v>
       </c>
     </row>
     <row r="43">
@@ -1452,20 +1452,20 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>8.013728559017181</v>
+        <v>9.117620289325714</v>
       </c>
       <c r="D43" t="n">
-        <v>2.592639667085117</v>
+        <v>2.500878391608261</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9497461676597595</v>
+        <v>0.9009859323501587</v>
       </c>
       <c r="F43" t="n">
-        <v>0.02773655097863584</v>
+        <v>0.0637240638387495</v>
       </c>
     </row>
     <row r="44">
@@ -1476,44 +1476,44 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8.035150095820427</v>
+        <v>9.166926890611649</v>
       </c>
       <c r="D44" t="n">
-        <v>4.887808188813858</v>
+        <v>2.329071644200221</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9314346551895142</v>
+        <v>0.9011556267738342</v>
       </c>
       <c r="F44" t="n">
-        <v>0.05927331522006938</v>
+        <v>0.05615198599776356</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GradientBoosting</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>8.038686619273918</v>
+        <v>9.261789545416832</v>
       </c>
       <c r="D45" t="n">
-        <v>3.205031349147639</v>
+        <v>2.088065239576141</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9504871029688371</v>
+        <v>0.8997485637664795</v>
       </c>
       <c r="F45" t="n">
-        <v>0.0292948689155439</v>
+        <v>0.04388415816998422</v>
       </c>
     </row>
     <row r="46">
@@ -1524,20 +1524,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.049855679273605</v>
+        <v>9.27982285618782</v>
       </c>
       <c r="D46" t="n">
-        <v>3.549223425376839</v>
+        <v>1.530339245729274</v>
       </c>
       <c r="E46" t="n">
-        <v>0.941627812385559</v>
+        <v>0.8732430934906006</v>
       </c>
       <c r="F46" t="n">
-        <v>0.04332258890309011</v>
+        <v>0.1158752772544542</v>
       </c>
     </row>
     <row r="47">
@@ -1552,16 +1552,16 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>8.102120757102966</v>
+        <v>9.304680153727531</v>
       </c>
       <c r="D47" t="n">
-        <v>4.503384337671496</v>
+        <v>3.10058565150685</v>
       </c>
       <c r="E47" t="n">
-        <v>0.926363718509674</v>
+        <v>0.894688856601715</v>
       </c>
       <c r="F47" t="n">
-        <v>0.06050333212706484</v>
+        <v>0.06954988128295814</v>
       </c>
     </row>
     <row r="48">
@@ -1572,116 +1572,116 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8.141273632645607</v>
+        <v>9.558940082788467</v>
       </c>
       <c r="D48" t="n">
-        <v>2.360406869479864</v>
+        <v>2.306046287255586</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9458651900291443</v>
+        <v>0.8898603439331054</v>
       </c>
       <c r="F48" t="n">
-        <v>0.02564280235372455</v>
+        <v>0.07135551167956704</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>8.183440119028091</v>
+        <v>9.605599045753479</v>
       </c>
       <c r="D49" t="n">
-        <v>2.57067264708434</v>
+        <v>2.350756992602456</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9505729436874389</v>
+        <v>0.8887346386909485</v>
       </c>
       <c r="F49" t="n">
-        <v>0.02395050859355196</v>
+        <v>0.06981290456108825</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Polynomial</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{"degree": 3, "alpha": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>8.264442011713982</v>
+        <v>9.644958110973782</v>
       </c>
       <c r="D50" t="n">
-        <v>6.482097521757519</v>
+        <v>2.860433729177997</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9317122817039489</v>
+        <v>0.8610780551452937</v>
       </c>
       <c r="F50" t="n">
-        <v>0.08266056329492093</v>
+        <v>0.07342256364307097</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 200, "max_depth": 2, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>8.315906003117561</v>
+        <v>9.69245821695316</v>
       </c>
       <c r="D51" t="n">
-        <v>2.567187741381979</v>
+        <v>3.025882016649667</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9384339809417724</v>
+        <v>0.8561692911579215</v>
       </c>
       <c r="F51" t="n">
-        <v>0.0369179931622664</v>
+        <v>0.08135432169459068</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>8.321506232023239</v>
+        <v>9.85627293586731</v>
       </c>
       <c r="D52" t="n">
-        <v>2.129126468777323</v>
+        <v>2.018784590314806</v>
       </c>
       <c r="E52" t="n">
-        <v>0.9493393898010254</v>
+        <v>0.888806962966919</v>
       </c>
       <c r="F52" t="n">
-        <v>0.01601484037108493</v>
+        <v>0.06183673303124346</v>
       </c>
     </row>
     <row r="53">
@@ -1692,20 +1692,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>8.365459591150284</v>
+        <v>9.857692271471024</v>
       </c>
       <c r="D53" t="n">
-        <v>3.369626293663592</v>
+        <v>2.802772935917928</v>
       </c>
       <c r="E53" t="n">
-        <v>0.9406421542167663</v>
+        <v>0.8861305832862854</v>
       </c>
       <c r="F53" t="n">
-        <v>0.04386796361100191</v>
+        <v>0.07150176017936721</v>
       </c>
     </row>
     <row r="54">
@@ -1720,400 +1720,400 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>8.377880752086639</v>
+        <v>9.878486767411232</v>
       </c>
       <c r="D54" t="n">
-        <v>2.617876600251932</v>
+        <v>2.824805973598751</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8906713366508484</v>
+        <v>0.8489822149276733</v>
       </c>
       <c r="F54" t="n">
-        <v>0.09639123311256619</v>
+        <v>0.09714831135874989</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.1}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>8.38854438964885</v>
+        <v>9.932973980903625</v>
       </c>
       <c r="D55" t="n">
-        <v>2.625084158092837</v>
+        <v>2.564575881215616</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9459945294553936</v>
+        <v>0.8430720210075379</v>
       </c>
       <c r="F55" t="n">
-        <v>0.02547386098191972</v>
+        <v>0.135216356721198</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>8.38854438964885</v>
+        <v>10.07374130189419</v>
       </c>
       <c r="D56" t="n">
-        <v>2.625084158092837</v>
+        <v>4.258609807149377</v>
       </c>
       <c r="E56" t="n">
-        <v>0.9459945294553936</v>
+        <v>0.8220464706420898</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02547386098191972</v>
+        <v>0.1458603245476987</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8.405147314106529</v>
+        <v>10.16758047219126</v>
       </c>
       <c r="D57" t="n">
-        <v>3.195479568246393</v>
+        <v>2.751599637391529</v>
       </c>
       <c r="E57" t="n">
-        <v>0.9410312025775653</v>
+        <v>0.8677814432588505</v>
       </c>
       <c r="F57" t="n">
-        <v>0.0388039041699386</v>
+        <v>0.07589399603085702</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>8.405147314106529</v>
+        <v>10.16758047219126</v>
       </c>
       <c r="D58" t="n">
-        <v>3.195479568246393</v>
+        <v>2.751599637391531</v>
       </c>
       <c r="E58" t="n">
-        <v>0.9410312025775653</v>
+        <v>0.8677814432588506</v>
       </c>
       <c r="F58" t="n">
-        <v>0.0388039041699386</v>
+        <v>0.07589399603085704</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>8.416044637560844</v>
+        <v>10.16758047219127</v>
       </c>
       <c r="D59" t="n">
-        <v>4.859624881689947</v>
+        <v>2.751599637391532</v>
       </c>
       <c r="E59" t="n">
-        <v>0.92561936378479</v>
+        <v>0.8677814432588505</v>
       </c>
       <c r="F59" t="n">
-        <v>0.07486199143457715</v>
+        <v>0.075893996030857</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>8.43106709420681</v>
+        <v>10.19265466904233</v>
       </c>
       <c r="D60" t="n">
-        <v>3.577790174950939</v>
+        <v>4.556094672996598</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9468420267105102</v>
+        <v>0.8230258076223343</v>
       </c>
       <c r="F60" t="n">
-        <v>0.03296473979527084</v>
+        <v>0.1483067779183022</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8.499853312969208</v>
+        <v>10.2044274217306</v>
       </c>
       <c r="D61" t="n">
-        <v>2.072524618837334</v>
+        <v>2.723707539584211</v>
       </c>
       <c r="E61" t="n">
-        <v>0.9451519608497619</v>
+        <v>0.869481827543064</v>
       </c>
       <c r="F61" t="n">
-        <v>0.01650196040715247</v>
+        <v>0.07532233601426444</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>8.54909211397171</v>
+        <v>10.2044274217306</v>
       </c>
       <c r="D62" t="n">
-        <v>3.102428345528724</v>
+        <v>2.723707539584211</v>
       </c>
       <c r="E62" t="n">
-        <v>0.8910308361053467</v>
+        <v>0.869481827543064</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1002540137760385</v>
+        <v>0.07532233601426444</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "leaky_relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>8.560394793748856</v>
+        <v>10.2044274217306</v>
       </c>
       <c r="D63" t="n">
-        <v>5.06653511639431</v>
+        <v>2.723707539584212</v>
       </c>
       <c r="E63" t="n">
-        <v>0.9211503624916076</v>
+        <v>0.869481827543064</v>
       </c>
       <c r="F63" t="n">
-        <v>0.08675281439147101</v>
+        <v>0.07532233601426443</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>8.628436031773315</v>
+        <v>10.21735854446888</v>
       </c>
       <c r="D64" t="n">
-        <v>4.180771868593259</v>
+        <v>4.446233784516075</v>
       </c>
       <c r="E64" t="n">
-        <v>0.9288428993060164</v>
+        <v>0.8216189265251159</v>
       </c>
       <c r="F64" t="n">
-        <v>0.06578490642742685</v>
+        <v>0.1461721103347907</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.05}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>8.628436031773315</v>
+        <v>10.2447597682476</v>
       </c>
       <c r="D65" t="n">
-        <v>4.180771868593259</v>
+        <v>1.616198606548454</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9288428993060164</v>
+        <v>0.8614335536956788</v>
       </c>
       <c r="F65" t="n">
-        <v>0.06578490642742685</v>
+        <v>0.08705508624945271</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>8.725060820579529</v>
+        <v>10.33083698137272</v>
       </c>
       <c r="D66" t="n">
-        <v>4.553228870532234</v>
+        <v>4.446246001537762</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9275112390518189</v>
+        <v>0.8229790033548463</v>
       </c>
       <c r="F66" t="n">
-        <v>0.05522471870604277</v>
+        <v>0.1385481410163488</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.1, "gamma": "scale"}</t>
+          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>8.742779328810039</v>
+        <v>10.34036642442328</v>
       </c>
       <c r="D67" t="n">
-        <v>2.684947342742644</v>
+        <v>2.78468901583117</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9322926930797368</v>
+        <v>0.8600116097378689</v>
       </c>
       <c r="F67" t="n">
-        <v>0.03578456290272591</v>
+        <v>0.08084935292107717</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>8.781193345785141</v>
+        <v>10.34036642442328</v>
       </c>
       <c r="D68" t="n">
-        <v>4.316097886663263</v>
+        <v>2.78468901583117</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9335535049438477</v>
+        <v>0.8600116097378689</v>
       </c>
       <c r="F68" t="n">
-        <v>0.05449443232887592</v>
+        <v>0.08084935292107716</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 5}</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8.818384483456612</v>
+        <v>10.34036642442329</v>
       </c>
       <c r="D69" t="n">
-        <v>3.260347756283567</v>
+        <v>2.78468901583117</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9182369112968445</v>
+        <v>0.8600116097378689</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04055873766110502</v>
+        <v>0.08084935292107716</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>8.898077156434169</v>
+        <v>10.54613975567452</v>
       </c>
       <c r="D70" t="n">
-        <v>4.40906275648804</v>
+        <v>3.063011216412048</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9190323730044836</v>
+        <v>0.8314984973090874</v>
       </c>
       <c r="F70" t="n">
-        <v>0.08139467025830434</v>
+        <v>0.1044220170807183</v>
       </c>
     </row>
     <row r="71">
@@ -2124,44 +2124,44 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>8.898077156434169</v>
+        <v>10.57922530733718</v>
       </c>
       <c r="D71" t="n">
-        <v>4.40906275648804</v>
+        <v>2.647080088244683</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9190323730044836</v>
+        <v>0.8571329470227113</v>
       </c>
       <c r="F71" t="n">
-        <v>0.08139467025830434</v>
+        <v>0.08098210457694843</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32, 16, 8], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8.914362713694572</v>
+        <v>10.57922530733718</v>
       </c>
       <c r="D72" t="n">
-        <v>4.772686585607411</v>
+        <v>2.647080088244683</v>
       </c>
       <c r="E72" t="n">
-        <v>0.9217795252799987</v>
+        <v>0.8571329470227113</v>
       </c>
       <c r="F72" t="n">
-        <v>0.07466787267664061</v>
+        <v>0.08098210457694843</v>
       </c>
     </row>
     <row r="73">
@@ -2172,284 +2172,284 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 2, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8.939329389972382</v>
+        <v>10.61317869516659</v>
       </c>
       <c r="D73" t="n">
-        <v>4.44783222907664</v>
+        <v>4.219074714917815</v>
       </c>
       <c r="E73" t="n">
-        <v>0.8977939601663076</v>
+        <v>0.8240918813289134</v>
       </c>
       <c r="F73" t="n">
-        <v>0.08541238939914012</v>
+        <v>0.1361756501840964</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>9.013927897878506</v>
+        <v>10.62024537570399</v>
       </c>
       <c r="D74" t="n">
-        <v>4.913770197960202</v>
+        <v>2.292130407886054</v>
       </c>
       <c r="E74" t="n">
-        <v>0.911738342431564</v>
+        <v>0.8689114576068608</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0971074180113807</v>
+        <v>0.06650668533247174</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>9.013927897878506</v>
+        <v>10.620245375704</v>
       </c>
       <c r="D75" t="n">
-        <v>4.913770197960202</v>
+        <v>2.292130407886054</v>
       </c>
       <c r="E75" t="n">
-        <v>0.911738342431564</v>
+        <v>0.8689114576068608</v>
       </c>
       <c r="F75" t="n">
-        <v>0.0971074180113807</v>
+        <v>0.06650668533247174</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 10.0, "epsilon": 0.5, "gamma": "scale"}</t>
+          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>9.024965058711389</v>
+        <v>10.620245375704</v>
       </c>
       <c r="D76" t="n">
-        <v>2.698972980632075</v>
+        <v>2.292130407886053</v>
       </c>
       <c r="E76" t="n">
-        <v>0.9301400930188114</v>
+        <v>0.8689114576068608</v>
       </c>
       <c r="F76" t="n">
-        <v>0.04010943380857634</v>
+        <v>0.06650668533247174</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.1, "gamma": "scale"}</t>
+          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>9.075047679689925</v>
+        <v>10.63580911777871</v>
       </c>
       <c r="D77" t="n">
-        <v>2.861137906846767</v>
+        <v>2.660832955883843</v>
       </c>
       <c r="E77" t="n">
-        <v>0.9152709868316137</v>
+        <v>0.8551764630049415</v>
       </c>
       <c r="F77" t="n">
-        <v>0.05300591727839519</v>
+        <v>0.07309394900224983</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>9.101362749934196</v>
+        <v>10.63580911777871</v>
       </c>
       <c r="D78" t="n">
-        <v>4.481201497900447</v>
+        <v>2.660832955883843</v>
       </c>
       <c r="E78" t="n">
-        <v>0.9327507257461548</v>
+        <v>0.8551764630049415</v>
       </c>
       <c r="F78" t="n">
-        <v>0.05290118337013553</v>
+        <v>0.07309394900224983</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16], "activation": "relu", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>9.282395914196968</v>
+        <v>10.68198108779851</v>
       </c>
       <c r="D79" t="n">
-        <v>4.349648377062304</v>
+        <v>2.23346568519318</v>
       </c>
       <c r="E79" t="n">
-        <v>0.9220166325569152</v>
+        <v>0.8697160047426861</v>
       </c>
       <c r="F79" t="n">
-        <v>0.05761042109258963</v>
+        <v>0.06561314922706667</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.5, "gamma": "scale"}</t>
+          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9.288930321233497</v>
+        <v>10.68198108779851</v>
       </c>
       <c r="D80" t="n">
-        <v>3.429825875353644</v>
+        <v>2.233465685193178</v>
       </c>
       <c r="E80" t="n">
-        <v>0.9154404552072466</v>
+        <v>0.8697160047426861</v>
       </c>
       <c r="F80" t="n">
-        <v>0.05467678461155759</v>
+        <v>0.06561314922706661</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Linear</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>{}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9.304376915097237</v>
+        <v>10.68367789141436</v>
       </c>
       <c r="D81" t="n">
-        <v>4.351541485199614</v>
+        <v>2.233316117284514</v>
       </c>
       <c r="E81" t="n">
-        <v>0.9119536399841308</v>
+        <v>0.8696754023947945</v>
       </c>
       <c r="F81" t="n">
-        <v>0.05517050155372261</v>
+        <v>0.06562851120404267</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9.380817785859108</v>
+        <v>10.6955423951149</v>
       </c>
       <c r="D82" t="n">
-        <v>3.783157261461371</v>
+        <v>4.232305791364705</v>
       </c>
       <c r="E82" t="n">
-        <v>0.8898111939430237</v>
+        <v>0.8176225662231446</v>
       </c>
       <c r="F82" t="n">
-        <v>0.08824699333502925</v>
+        <v>0.1481383080309528</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9.544342385833456</v>
+        <v>10.71017103139445</v>
       </c>
       <c r="D83" t="n">
-        <v>5.779321218573862</v>
+        <v>2.332101452915877</v>
       </c>
       <c r="E83" t="n">
-        <v>0.8849785362342499</v>
+        <v>0.8620977625416533</v>
       </c>
       <c r="F83" t="n">
-        <v>0.1365244801780816</v>
+        <v>0.07118211568701228</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>LightGBM</t>
+          <t>RandomForest</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9.544342385833456</v>
+        <v>10.71017103139445</v>
       </c>
       <c r="D84" t="n">
-        <v>5.779321218573862</v>
+        <v>2.332101452915878</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8849785362342499</v>
+        <v>0.8620977625416533</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1365244801780816</v>
+        <v>0.07118211568701228</v>
       </c>
     </row>
     <row r="85">
@@ -2460,260 +2460,260 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 2}</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9.906445611374796</v>
+        <v>10.71017103139445</v>
       </c>
       <c r="D85" t="n">
-        <v>6.047002511883136</v>
+        <v>2.33210145291588</v>
       </c>
       <c r="E85" t="n">
-        <v>0.9077615886543688</v>
+        <v>0.8620977625416533</v>
       </c>
       <c r="F85" t="n">
-        <v>0.101456311340782</v>
+        <v>0.07118211568701233</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 100, "max_depth": 3, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9.906445611374796</v>
+        <v>10.72720900177956</v>
       </c>
       <c r="D86" t="n">
-        <v>6.047002511883135</v>
+        <v>4.207447232052396</v>
       </c>
       <c r="E86" t="n">
-        <v>0.9077615886543688</v>
+        <v>0.8219509124755859</v>
       </c>
       <c r="F86" t="n">
-        <v>0.101456311340782</v>
+        <v>0.1431500471151892</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 5}</t>
+          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9.906445611374798</v>
+        <v>10.75894698500633</v>
       </c>
       <c r="D87" t="n">
-        <v>6.047002511883135</v>
+        <v>3.958304922226807</v>
       </c>
       <c r="E87" t="n">
-        <v>0.9077615886543688</v>
+        <v>0.8006073951721191</v>
       </c>
       <c r="F87" t="n">
-        <v>0.101456311340782</v>
+        <v>0.1725018307769849</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>GradientBoosting</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>10.00043739597968</v>
+        <v>10.85850647151403</v>
       </c>
       <c r="D88" t="n">
-        <v>6.175389098296201</v>
+        <v>4.56870069583396</v>
       </c>
       <c r="E88" t="n">
-        <v>0.9041315709991797</v>
+        <v>0.8072064292850311</v>
       </c>
       <c r="F88" t="n">
-        <v>0.108421374685966</v>
+        <v>0.1641389568494649</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 5}</t>
+          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>10.00043739597968</v>
+        <v>10.91784730553627</v>
       </c>
       <c r="D89" t="n">
-        <v>6.175389098296201</v>
+        <v>2.187483388579762</v>
       </c>
       <c r="E89" t="n">
-        <v>0.9041315709991797</v>
+        <v>0.8522172331809997</v>
       </c>
       <c r="F89" t="n">
-        <v>0.108421374685966</v>
+        <v>0.06869955634912682</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 100, "max_depth": -1, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>10.00043739597968</v>
+        <v>10.93990932547145</v>
       </c>
       <c r="D90" t="n">
-        <v>6.175389098296198</v>
+        <v>3.00072331891775</v>
       </c>
       <c r="E90" t="n">
-        <v>0.9041315709991797</v>
+        <v>0.8465231740983835</v>
       </c>
       <c r="F90" t="n">
-        <v>0.108421374685966</v>
+        <v>0.08175944596567666</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>{"architecture": [128, 64, 32], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 100, "max_depth": 10, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>10.0418334454298</v>
+        <v>10.93990932547145</v>
       </c>
       <c r="D91" t="n">
-        <v>3.050089668475285</v>
+        <v>3.00072331891775</v>
       </c>
       <c r="E91" t="n">
-        <v>0.8884872198104858</v>
+        <v>0.8465231740983835</v>
       </c>
       <c r="F91" t="n">
-        <v>0.08357055847393464</v>
+        <v>0.08175944596567666</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>10.04232138395309</v>
+        <v>10.9992553293705</v>
       </c>
       <c r="D92" t="n">
-        <v>2.428188562120639</v>
+        <v>4.155357305108748</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7552256345748901</v>
+        <v>0.8147426962852478</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1976844023840033</v>
+        <v>0.1443576204381755</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10.04447084841718</v>
+        <v>11.02072224838601</v>
       </c>
       <c r="D93" t="n">
-        <v>6.008338221345805</v>
+        <v>3.132193513308991</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9056367616163629</v>
+        <v>0.845557594694854</v>
       </c>
       <c r="F93" t="n">
-        <v>0.1038415145983047</v>
+        <v>0.09795031857834288</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 5}</t>
+          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>10.04447084841718</v>
+        <v>11.02072224838601</v>
       </c>
       <c r="D94" t="n">
-        <v>6.008338221345805</v>
+        <v>3.132193513308991</v>
       </c>
       <c r="E94" t="n">
-        <v>0.9056367616163626</v>
+        <v>0.845557594694854</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1038415145983047</v>
+        <v>0.09795031857834288</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 5}</t>
+          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>10.04447084841718</v>
+        <v>11.03443585266128</v>
       </c>
       <c r="D95" t="n">
-        <v>6.008338221345803</v>
+        <v>1.754238281882234</v>
       </c>
       <c r="E95" t="n">
-        <v>0.9056367616163626</v>
+        <v>0.8645287159151647</v>
       </c>
       <c r="F95" t="n">
-        <v>0.1038415145983046</v>
+        <v>0.06749968261609526</v>
       </c>
     </row>
     <row r="96">
@@ -2724,260 +2724,260 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>{"architecture": [32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>10.25932446122169</v>
+        <v>11.07795678079128</v>
       </c>
       <c r="D96" t="n">
-        <v>1.899857738170673</v>
+        <v>5.637193850920977</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7572998881340027</v>
+        <v>0.79597989320755</v>
       </c>
       <c r="F96" t="n">
-        <v>0.1608279259236283</v>
+        <v>0.2195875838236394</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": null, "min_samples_split": 2}</t>
+          <t>{"degree": 3, "alpha": 10.0}</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>10.82439317839873</v>
+        <v>11.08451440930367</v>
       </c>
       <c r="D97" t="n">
-        <v>5.472523830331353</v>
+        <v>2.800228763963932</v>
       </c>
       <c r="E97" t="n">
-        <v>0.8985522556211146</v>
+        <v>0.847779381275177</v>
       </c>
       <c r="F97" t="n">
-        <v>0.08687785530987233</v>
+        <v>0.1140520546865875</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 20, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 200, "max_depth": 10, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>10.82439317839873</v>
+        <v>11.29111857040036</v>
       </c>
       <c r="D98" t="n">
-        <v>5.472523830331356</v>
+        <v>3.552119873801909</v>
       </c>
       <c r="E98" t="n">
-        <v>0.8985522556211146</v>
+        <v>0.8371635928434905</v>
       </c>
       <c r="F98" t="n">
-        <v>0.08687785530987237</v>
+        <v>0.1005061061374938</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 10, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 200, "max_depth": -1, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>10.82588239865216</v>
+        <v>11.29111857040036</v>
       </c>
       <c r="D99" t="n">
-        <v>5.471808405833574</v>
+        <v>3.552119873801909</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8985205233350968</v>
+        <v>0.8371635928434905</v>
       </c>
       <c r="F99" t="n">
-        <v>0.08686174621011221</v>
+        <v>0.1005061061374938</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 20, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 300, "max_depth": 3, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>10.91942717472925</v>
+        <v>11.37966245412827</v>
       </c>
       <c r="D100" t="n">
-        <v>5.622440745178431</v>
+        <v>4.237748237909501</v>
       </c>
       <c r="E100" t="n">
-        <v>0.8956604814173718</v>
+        <v>0.8132238984107971</v>
       </c>
       <c r="F100" t="n">
-        <v>0.09328338930598913</v>
+        <v>0.1421387672425686</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": null, "min_samples_split": 2}</t>
+          <t>{"kernel": "rbf", "C": 100.0, "epsilon": 0.5, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>10.91942717472925</v>
+        <v>11.46364857404654</v>
       </c>
       <c r="D101" t="n">
-        <v>5.622440745178429</v>
+        <v>2.1997584976633</v>
       </c>
       <c r="E101" t="n">
-        <v>0.8956604814173718</v>
+        <v>0.8639564453611071</v>
       </c>
       <c r="F101" t="n">
-        <v>0.09328338930598912</v>
+        <v>0.07487820359588744</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 10, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 300, "max_depth": -1, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>10.9216610051094</v>
+        <v>11.57381983944995</v>
       </c>
       <c r="D102" t="n">
-        <v>5.621357002415492</v>
+        <v>3.419061753785285</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8956135596254491</v>
+        <v>0.8265551738240582</v>
       </c>
       <c r="F102" t="n">
-        <v>0.09325951757328653</v>
+        <v>0.1115753486233063</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": null, "min_samples_split": 2}</t>
+          <t>{"n_estimators": 300, "max_depth": 10, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>10.98618425918465</v>
+        <v>11.57381983944995</v>
       </c>
       <c r="D103" t="n">
-        <v>5.490679353223732</v>
+        <v>3.419061753785285</v>
       </c>
       <c r="E103" t="n">
-        <v>0.8955137892506331</v>
+        <v>0.8265551738240582</v>
       </c>
       <c r="F103" t="n">
-        <v>0.08996675810060867</v>
+        <v>0.1115753486233063</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>Linear</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 20, "min_samples_split": 2}</t>
+          <t>{}</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>10.98618425918465</v>
+        <v>11.80046081542969</v>
       </c>
       <c r="D104" t="n">
-        <v>5.490679353223734</v>
+        <v>2.971259501229719</v>
       </c>
       <c r="E104" t="n">
-        <v>0.8955137892506331</v>
+        <v>0.8726012229919433</v>
       </c>
       <c r="F104" t="n">
-        <v>0.08996675810060867</v>
+        <v>0.07966658708770274</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>RandomForest</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 10, "min_samples_split": 2}</t>
+          <t>{"degree": 3, "alpha": 1.0}</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>10.98889712535618</v>
+        <v>12.03520551323891</v>
       </c>
       <c r="D105" t="n">
-        <v>5.489072307316332</v>
+        <v>3.620714810688878</v>
       </c>
       <c r="E105" t="n">
-        <v>0.8954897508789792</v>
+        <v>0.7914129972457886</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0899592275289928</v>
+        <v>0.1804742548465659</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Polynomial</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.05}</t>
+          <t>{"degree": 3, "alpha": 0.1}</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>11.31426364183426</v>
+        <v>12.28484079241753</v>
       </c>
       <c r="D106" t="n">
-        <v>5.864758945853649</v>
+        <v>3.83582989043074</v>
       </c>
       <c r="E106" t="n">
-        <v>0.8799492120742798</v>
+        <v>0.7804380655288696</v>
       </c>
       <c r="F106" t="n">
-        <v>0.1083077226300908</v>
+        <v>0.1917467782848915</v>
       </c>
     </row>
     <row r="107">
@@ -2988,44 +2988,44 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>11.35791525244713</v>
+        <v>12.38336071372032</v>
       </c>
       <c r="D107" t="n">
-        <v>5.264501416265238</v>
+        <v>3.218178435656313</v>
       </c>
       <c r="E107" t="n">
-        <v>0.8817597627639771</v>
+        <v>0.823523998260498</v>
       </c>
       <c r="F107" t="n">
-        <v>0.10017828290326</v>
+        <v>0.111819361092051</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.05}</t>
+          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.1, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>11.40349105000496</v>
+        <v>12.8341340983828</v>
       </c>
       <c r="D108" t="n">
-        <v>5.493804575676863</v>
+        <v>2.082204521982699</v>
       </c>
       <c r="E108" t="n">
-        <v>0.8790944576263428</v>
+        <v>0.8616866001714666</v>
       </c>
       <c r="F108" t="n">
-        <v>0.1032615417133403</v>
+        <v>0.07015037604933978</v>
       </c>
     </row>
     <row r="109">
@@ -3036,44 +3036,44 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.1}</t>
+          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>11.41244381666183</v>
+        <v>12.93473973870277</v>
       </c>
       <c r="D109" t="n">
-        <v>5.256744095791677</v>
+        <v>3.444462342269337</v>
       </c>
       <c r="E109" t="n">
-        <v>0.8799449324607849</v>
+        <v>0.8102392673492431</v>
       </c>
       <c r="F109" t="n">
-        <v>0.09883464177235801</v>
+        <v>0.117770178240053</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>SVR</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.1}</t>
+          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.5, "gamma": "scale"}</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>11.42117097973824</v>
+        <v>13.03234247765927</v>
       </c>
       <c r="D110" t="n">
-        <v>5.245957063234639</v>
+        <v>2.0472196937613</v>
       </c>
       <c r="E110" t="n">
-        <v>0.8800473093986512</v>
+        <v>0.857870541866426</v>
       </c>
       <c r="F110" t="n">
-        <v>0.09883748801454395</v>
+        <v>0.06848538755382078</v>
       </c>
     </row>
     <row r="111">
@@ -3084,92 +3084,92 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.05}</t>
+          <t>{"n_estimators": 100, "max_depth": 6, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>11.49052694439888</v>
+        <v>13.03434669971466</v>
       </c>
       <c r="D111" t="n">
-        <v>5.47037468999241</v>
+        <v>2.855988090711969</v>
       </c>
       <c r="E111" t="n">
-        <v>0.8775258183479309</v>
+        <v>0.8080790758132934</v>
       </c>
       <c r="F111" t="n">
-        <v>0.103336226937111</v>
+        <v>0.1040403994758643</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.5, "gamma": "scale"}</t>
+          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.05}</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>12.48094643080767</v>
+        <v>13.13331559300423</v>
       </c>
       <c r="D112" t="n">
-        <v>6.559823953439544</v>
+        <v>3.494382696245002</v>
       </c>
       <c r="E112" t="n">
-        <v>0.8418600466819285</v>
+        <v>0.8065690755844116</v>
       </c>
       <c r="F112" t="n">
-        <v>0.09009377584183918</v>
+        <v>0.1180238412851277</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SVR</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>{"kernel": "rbf", "C": 1.0, "epsilon": 0.1, "gamma": "scale"}</t>
+          <t>{"n_estimators": 200, "max_depth": 6, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>12.796759377906</v>
+        <v>13.38289439678192</v>
       </c>
       <c r="D113" t="n">
-        <v>7.204585811759382</v>
+        <v>2.914575453197918</v>
       </c>
       <c r="E113" t="n">
-        <v>0.8388100129997221</v>
+        <v>0.8003476381301879</v>
       </c>
       <c r="F113" t="n">
-        <v>0.09532400156995881</v>
+        <v>0.1027568385683677</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
+          <t>{"n_estimators": 300, "max_depth": 6, "learning_rate": 0.1}</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>44.56011742353439</v>
+        <v>13.40973347425461</v>
       </c>
       <c r="D114" t="n">
-        <v>16.53828874626423</v>
+        <v>2.911588821959727</v>
       </c>
       <c r="E114" t="n">
-        <v>-0.2818889379501343</v>
+        <v>0.7999986290931702</v>
       </c>
       <c r="F114" t="n">
-        <v>0.4253231965491649</v>
+        <v>0.1024215932976491</v>
       </c>
     </row>
     <row r="115">
@@ -3180,20 +3180,20 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.1}</t>
+          <t>{"architecture": [64, 32, 16, 8], "activation": "tanh", "learning_rate": 0.001, "dropout_rate": 0.0}</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>44.7474279999733</v>
+        <v>30.24241879582405</v>
       </c>
       <c r="D115" t="n">
-        <v>16.83025230975592</v>
+        <v>16.74024249387064</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.3230811595916748</v>
+        <v>0.2025382041931152</v>
       </c>
       <c r="F115" t="n">
-        <v>0.4239149639771049</v>
+        <v>0.509957473663012</v>
       </c>
     </row>
     <row r="116">
@@ -3208,16 +3208,16 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>44.76057022809982</v>
+        <v>46.17955267429352</v>
       </c>
       <c r="D116" t="n">
-        <v>16.71525286154597</v>
+        <v>10.83720537040873</v>
       </c>
       <c r="E116" t="n">
-        <v>-0.2763402462005615</v>
+        <v>-0.1536699056625366</v>
       </c>
       <c r="F116" t="n">
-        <v>0.4299319483790596</v>
+        <v>0.1704842315462392</v>
       </c>
     </row>
     <row r="117">
@@ -3232,16 +3232,16 @@
         </is>
       </c>
       <c r="C117" t="n">
-        <v>45.04330635070801</v>
+        <v>46.72514021396637</v>
       </c>
       <c r="D117" t="n">
-        <v>16.50977939482123</v>
+        <v>11.15957945826675</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.2697826385498047</v>
+        <v>-0.1608327150344849</v>
       </c>
       <c r="F117" t="n">
-        <v>0.4318451074572773</v>
+        <v>0.1568756043580084</v>
       </c>
     </row>
   </sheetData>
